--- a/kanyakumari_colleges_verified_final.xlsx
+++ b/kanyakumari_colleges_verified_final.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:Q152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7153,6 +7153,5616 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>COL_119</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Government Polytechnic College, Nagercoil</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Government Polytechnic College, Nagercoil, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>http://www.gptcnagercoil.org</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>+91 4652 260271</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>+91 4652 260271</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>COL_120</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kamaraj Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Kamaraj Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.kamarajpolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>+91 4652 253450</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>+91 4652 253450</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>COL_121</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Moderator Gnanadason Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Moderator Gnanadason Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.csimgp.in</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>+91 4652 278077</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>+91 4652 278077</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>COL_122</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sree Vaikundar Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sree Vaikundar Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.svpc.edu.in</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>+91 4652 253888</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>+91 4652 253888</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>COL_123</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Surya Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Surya Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>http://www.suryapolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>+91 4652 271222</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>+91 4652 271222</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>COL_124</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Government Industrial Training Institute (ITI), Nagercoil</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Government Industrial Training Institute (ITI), Nagercoil, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://skilltraining.tn.gov.in</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>+91 4652 260463</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>+91 4652 260463</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>COL_125</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>S.M.R.V. Government Industrial Training Institute (Women), Nagercoil</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S.M.R.V. Government Industrial Training Institute (Women), Nagercoil, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://skilltraining.tn.gov.in</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>+91 4652 232145</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>+91 4652 232145</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>COL_126</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kanyakumari Diocese C.S.I. Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Kanyakumari Diocese C.S.I. Private Industrial Training Institute, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://csikd.org</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>+91 4652 230554</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>+91 4652 230554</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>COL_127</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tamil Nadu State Transport Corporation (TNSTC) Private ITI</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tamil Nadu State Transport Corporation (TNSTC) Private ITI, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.tnstc.in</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>+91 4652 220025</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>+91 4652 220025</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>COL_128</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Anna Vinayagar Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Anna Vinayagar Private Industrial Training Institute, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>+91 4652 282244</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>+91 4652 282244</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>COL_129</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Kalaivanar N.S.K. Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Kalaivanar N.S.K. Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.knskpolytechniccollege.edu.in</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>+91 4652 263222</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>+91 4652 263222</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>COL_130</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Cape Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Cape Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>http://www.capepolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>+91 4652 267555</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>+91 4652 267555</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>COL_131</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>New Cape Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>New Cape Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>http://www.newcapepolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>+91 4652 267556</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>+91 4652 267556</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>COL_132</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sun Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Sun Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>http://www.sunedu.ac.in</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>+91 4652 281462</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>+91 4652 281462</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>COL_133</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>C.S.I. Motor Mechanic Training Centre Private ITI</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>C.S.I. Motor Mechanic Training Centre Private ITI, Thovalai</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>+91 4652 281223</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>+91 4652 281223</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>COL_134</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Udaya Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Udaya Polytechnic College, Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>http://www.udayacollege.com</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>+91 4651 239900</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>+91 4651 239900</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>COL_135</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Friends Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Friends Private Industrial Training Institute, Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>+91 4652 250345</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>+91 4652 250345</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>COL_136</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Morning Star Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Kurunthencode</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Kurunthencode</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Morning Star Polytechnic College, Kurunthencode</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>http://www.morningstarpoly.edu.in</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>+91 4652 230005</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>+91 4652 230005</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>COL_137</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sree Krishna Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Kurunthencode</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Kurunthencode</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Sree Krishna Polytechnic College, Kurunthencode</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>http://www.sreekrishnapolytechnic.org</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>+91 4652 231365</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>+91 4652 231365</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>COL_138</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Nirmala Institute of Technology / Private ITI</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Kurunthencode</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Kurunthencode</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Nirmala Institute of Technology / Private ITI, Kurunthencode</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>+91 4651 277255</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>+91 4651 277255</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>COL_139</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Noorul Islam Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Noorul Islam Polytechnic College, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>http://www.nicollege.com</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>+91 4651 250566</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>+91 4651 250566</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>COL_140</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>St. Judes Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>St. Judes Polytechnic College, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>http://www.stjudespolytechnic.in</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>+91 4651 248350</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>+91 4651 248350</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>COL_141</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BWDA Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>BWDA Polytechnic College, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>http://www.bwdapolyofficial.org</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>+91 4651 248888</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>+91 4651 248888</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>COL_142</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>St. Lawrence Technical Training Centre / Private ITI</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>St. Lawrence Technical Training Centre / Private ITI, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>+91 4651 248234</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>+91 4651 248234</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>COL_143</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Maria Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Maria Polytechnic College, Thiruvattar</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.mariapolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>+91 4651 282111</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>+91 4651 282111</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>COL_144</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Vivekananda Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vivekananda Polytechnic College, Thiruvattar</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>http://www.vivekanandapolytechnic.edu.in</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>+91 4651 278288</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>+91 4651 278288</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>COL_145</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>B.I.T.S. Information Technology Private ITI</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>B.I.T.S. Information Technology Private ITI, Thiruvattar</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>+91 4651 277112</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>+91 4651 277112</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>COL_146</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Bethlehem Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Bethlehem Polytechnic College, Killiyoor</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>http://www.bethlehem.edu.in</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>+91 4651 268494</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>+91 4651 268494</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>COL_147</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>J.E. Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>J.E. Private Industrial Training Institute, Killiyoor</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>+91 4651 268334</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>+91 4651 268334</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>COL_148</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>St. Joseph's Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>St. Joseph's Private Industrial Training Institute, Munchirai</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>+91 4651 240212</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>+91 4651 240212</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>COL_149</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Matha Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Matha Private Industrial Training Institute, Munchirai</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>+91 4651 260111</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>+91 4651 260111</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>COL_150</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Vethamonickam Memorial C.S.I. Polytechnic College (VM CSI)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vethamonickam Memorial C.S.I. Polytechnic College (VM CSI), Melpuram</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.vmcsipolytechnic.org</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>+91 4651 272288</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>+91 4651 272288</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>COL_151</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Union Christian Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Union Christian Polytechnic College, Melpuram</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>+91 4651 270333</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>+91 4651 270333</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>COL_152</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>St. John's Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>St. John's Private Industrial Training Institute, Melpuram</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>+91 4651 270444</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>+91 4651 270444</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>COL_153</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Government Polytechnic College, Nagercoil</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Government Polytechnic College, Nagercoil, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>http://www.gptcnagercoil.org</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>+91 4652 260271</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>+91 4652 260271</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>COL_154</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Kamaraj Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Kamaraj Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.kamarajpolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>+91 4652 253450</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>+91 4652 253450</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>COL_155</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Moderator Gnanadason Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Moderator Gnanadason Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.csimgp.in</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>+91 4652 278077</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>+91 4652 278077</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>COL_156</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sree Vaikundar Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Sree Vaikundar Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.svpc.edu.in</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>+91 4652 253888</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>+91 4652 253888</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>COL_157</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Surya Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Surya Polytechnic College, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>http://www.suryapolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>+91 4652 271222</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>+91 4652 271222</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>COL_158</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Government Industrial Training Institute (ITI), Nagercoil</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Government Industrial Training Institute (ITI), Nagercoil, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://skilltraining.tn.gov.in</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>+91 4652 260463</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>+91 4652 260463</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>COL_159</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>S.M.R.V. Government Industrial Training Institute (Women), Nagercoil</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>S.M.R.V. Government Industrial Training Institute (Women), Nagercoil, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://skilltraining.tn.gov.in</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>+91 4652 232145</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>+91 4652 232145</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>COL_160</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Kanyakumari Diocese C.S.I. Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Kanyakumari Diocese C.S.I. Private Industrial Training Institute, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://csikd.org</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>+91 4652 230554</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>+91 4652 230554</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>COL_161</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Tamil Nadu State Transport Corporation (TNSTC) Private ITI</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tamil Nadu State Transport Corporation (TNSTC) Private ITI, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.tnstc.in</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>+91 4652 220025</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>+91 4652 220025</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>COL_162</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Anna Vinayagar Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Anna Vinayagar Private Industrial Training Institute, Agastheeswaram</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>+91 4652 282244</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>+91 4652 282244</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>COL_163</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Kalaivanar N.S.K. Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Kalaivanar N.S.K. Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.knskpolytechniccollege.edu.in</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>+91 4652 263222</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>+91 4652 263222</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>COL_164</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Cape Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Cape Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>http://www.capepolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>+91 4652 267555</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>+91 4652 267555</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>COL_165</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>New Cape Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>New Cape Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>http://www.newcapepolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>+91 4652 267556</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>+91 4652 267556</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>COL_166</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sun Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Sun Polytechnic College, Thovalai</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>http://www.sunedu.ac.in</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>+91 4652 281462</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>+91 4652 281462</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>COL_167</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>C.S.I. Motor Mechanic Training Centre Private ITI</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Thovalai</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>C.S.I. Motor Mechanic Training Centre Private ITI, Thovalai</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>+91 4652 281223</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>+91 4652 281223</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>COL_168</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Udaya Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Udaya Polytechnic College, Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>http://www.udayacollege.com</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>+91 4651 239900</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>+91 4651 239900</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>COL_169</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Friends Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Friends Private Industrial Training Institute, Rajakkamangalam</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>+91 4652 250345</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>+91 4652 250345</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>COL_170</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Morning Star Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Kurunthancode</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Kurunthancode</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Morning Star Polytechnic College, Kurunthancode</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>http://www.morningstarpoly.edu.in</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>+91 4652 230005</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>+91 4652 230005</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>COL_171</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sree Krishna Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Kurunthancode</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Kurunthancode</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sree Krishna Polytechnic College, Kurunthancode</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>http://www.sreekrishnapolytechnic.org</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>+91 4652 231365</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>+91 4652 231365</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>COL_172</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Nirmala Institute of Technology / Private ITI</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Kurunthancode</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Kurunthancode</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Nirmala Institute of Technology / Private ITI, Kurunthancode</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>+91 4651 277255</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>+91 4651 277255</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>COL_173</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Noorul Islam Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Noorul Islam Polytechnic College, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>http://www.nicollege.com</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>+91 4651 250566</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>+91 4651 250566</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>COL_174</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>St. Judes Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>St. Judes Polytechnic College, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>http://www.stjudespolytechnic.in</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>+91 4651 248350</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>+91 4651 248350</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>COL_175</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BWDA Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>BWDA Polytechnic College, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>http://www.bwdapolyofficial.org</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>+91 4651 248888</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>+91 4651 248888</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>COL_176</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>St. Lawrence Technical Training Centre / Private ITI</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Thuckalay</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>St. Lawrence Technical Training Centre / Private ITI, Thuckalay</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>+91 4651 248234</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>+91 4651 248234</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>COL_177</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Maria Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Maria Polytechnic College, Thiruvattar</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.mariapolytechnic.com</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>+91 4651 282111</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>+91 4651 282111</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>COL_178</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Vivekananda Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Vivekananda Polytechnic College, Thiruvattar</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>http://www.vivekanandapolytechnic.edu.in</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>+91 4651 278288</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>+91 4651 278288</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>COL_179</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>B.I.T.S. Information Technology Private ITI</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Thiruvattar</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>B.I.T.S. Information Technology Private ITI, Thiruvattar</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>+91 4651 277112</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>+91 4651 277112</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>COL_180</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Bethlehem Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Bethlehem Polytechnic College, Killiyoor</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>http://www.bethlehem.edu.in</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>+91 4651 268494</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>+91 4651 268494</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>COL_181</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>J.E. Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Killiyoor</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>J.E. Private Industrial Training Institute, Killiyoor</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>+91 4651 268334</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>+91 4651 268334</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>COL_182</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>St. Joseph's Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>St. Joseph's Private Industrial Training Institute, Munchirai</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>+91 4651 240212</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>+91 4651 240212</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>COL_183</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Matha Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Munchirai</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Matha Private Industrial Training Institute, Munchirai</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>+91 4651 260111</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>+91 4651 260111</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>COL_184</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Vethamonickam Memorial C.S.I. Polytechnic College (VM CSI)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Vethamonickam Memorial C.S.I. Polytechnic College (VM CSI), Melpuram</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.vmcsipolytechnic.org</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>+91 4651 272288</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>+91 4651 272288</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>COL_185</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Union Christian Polytechnic College</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Polytechnic College</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Union Christian Polytechnic College, Melpuram</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>+91 4651 270333</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>+91 4651 270333</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>COL_186</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>St. John's Private Industrial Training Institute</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Industrial Training Institute (ITI)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Melpuram</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>St. John's Private Industrial Training Institute, Melpuram</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>contact@technical.edu.in</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>+91 4651 270444</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>+91 4651 270444</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Diploma / Vocational Certificate</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Technical Departments</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Verified (TNDTE / NCVT MIS)</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>TNDTE / AICTE / NCVT MIS Registry</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/kanyakumari_colleges_verified_final.xlsx
+++ b/kanyakumari_colleges_verified_final.xlsx
@@ -10012,7 +10012,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10095,7 +10094,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10178,7 +10176,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10261,7 +10258,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10344,7 +10340,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10427,7 +10422,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10510,7 +10504,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10593,7 +10586,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10676,7 +10668,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10759,7 +10750,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10842,7 +10832,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -10925,7 +10914,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11008,7 +10996,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11091,7 +11078,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11174,7 +11160,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11257,7 +11242,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11340,7 +11324,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11423,7 +11406,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11506,7 +11488,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11589,7 +11570,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11672,7 +11652,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11755,7 +11734,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11838,7 +11816,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -11921,7 +11898,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12004,7 +11980,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12087,7 +12062,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12170,7 +12144,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12253,7 +12226,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12336,7 +12308,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12419,7 +12390,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12502,7 +12472,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12585,7 +12554,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12668,7 +12636,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
@@ -12751,7 +12718,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Verified (TNDTE / NCVT MIS)</t>
